--- a/sections_config_mac.xlsx
+++ b/sections_config_mac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13a0fd42d83c08bf/Documents/Cursos/ILLINOIS/IE_421_High_Frequency_Trading/LinuxVM/LLM_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{17DEADED-3F36-7A45-9954-13B779C8B78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5760F9-EFAD-FC4A-88F9-D29D7119BF1D}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{17DEADED-3F36-7A45-9954-13B779C8B78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DC4B18E-E2D4-DA4C-94F6-F73923F44064}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1660" windowWidth="27240" windowHeight="16160" xr2:uid="{D840E18A-208A-1543-8781-3BD2E5582C66}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sections!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
   <si>
     <t>Section_Title</t>
   </si>
@@ -228,6 +228,45 @@
   </si>
   <si>
     <t>Custom Metric</t>
+  </si>
+  <si>
+    <t>BIOS &amp; Firmware</t>
+  </si>
+  <si>
+    <t>BIOS Version &amp; Date</t>
+  </si>
+  <si>
+    <t>system_profiler SPHardwareDataType | grep -E "Boot ROM Version|SMC"</t>
+  </si>
+  <si>
+    <t>Motherboard &amp; Chipset</t>
+  </si>
+  <si>
+    <t>system_profiler SPHardwareDataType SPSoftwareDataType | grep -E "Model|Chipset"</t>
+  </si>
+  <si>
+    <t>CPU Power States</t>
+  </si>
+  <si>
+    <t>Idle States &amp; Frequency</t>
+  </si>
+  <si>
+    <t>PCIe / Thunderbolt Power</t>
+  </si>
+  <si>
+    <t>system_profiler SPPCIeDataType | grep -E "Power|Link" 2&gt;/dev/null</t>
+  </si>
+  <si>
+    <t>CPU Flags &amp; Features</t>
+  </si>
+  <si>
+    <t>sysctl -n machdep.cpu.features | cat</t>
+  </si>
+  <si>
+    <t>powermetrics -n 1 --samplers cpu_power | grep -i "residency"</t>
+  </si>
+  <si>
+    <t>powermetrics --samplers cpu_power -n 1</t>
   </si>
 </sst>
 </file>
@@ -297,10 +336,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F98F07-8A77-3547-A6A2-1E1EBA77126D}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
@@ -1065,6 +1100,114 @@
         <v>20</v>
       </c>
     </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{F7F98F07-8A77-3547-A6A2-1E1EBA77126D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
